--- a/01_Foundations_Data_Entry_and_Navigation.xlsx
+++ b/01_Foundations_Data_Entry_and_Navigation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HUNANI TRADING CO\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD91639-EF29-4A0D-B8A5-081DC47043D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D950F72B-1B4A-480F-ABFA-32CE3287D058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4425" yWindow="2820" windowWidth="15375" windowHeight="7980" xr2:uid="{C1392471-38FB-40FB-8F89-CDCC841DD498}"/>
+    <workbookView xWindow="4425" yWindow="2820" windowWidth="15375" windowHeight="7980" activeTab="1" xr2:uid="{C1392471-38FB-40FB-8F89-CDCC841DD498}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Taking_Charge" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="60">
   <si>
     <t>Updated</t>
   </si>
@@ -134,9 +134,6 @@
     <t>Order No</t>
   </si>
   <si>
-    <t xml:space="preserve">Fill month wise using autofill option </t>
-  </si>
-  <si>
     <t>Fill values by using Flash fill option with (ctrl+E)</t>
   </si>
   <si>
@@ -219,6 +216,12 @@
   </si>
   <si>
     <t>Separate first name &amp; last name by using flash fill (ctrl+E), Auto Fill Options.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fill month wise by using "Auto Fill Options" from Fill Handle </t>
+  </si>
+  <si>
+    <t>Use =SUM Formula to Total Cost</t>
   </si>
 </sst>
 </file>
@@ -281,8 +284,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1" tint="0.14999847407452621"/>
+      <sz val="10"/>
+      <color theme="1" tint="0.34998626667073579"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -333,7 +336,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -345,14 +348,17 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -763,9 +769,6 @@
       <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
       <c r="E7" t="s">
         <v>5</v>
       </c>
@@ -777,9 +780,6 @@
       <c r="A8" t="s">
         <v>4</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
       <c r="E8" t="s">
         <v>4</v>
       </c>
@@ -802,9 +802,6 @@
       <c r="A10" t="s">
         <v>2</v>
       </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
       <c r="E10" t="s">
         <v>2</v>
       </c>
@@ -815,6 +812,9 @@
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
       </c>
       <c r="E11" t="s">
         <v>1</v>
@@ -845,7 +845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D30709B7-3BFA-4931-805C-2F97B2689E42}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -899,6 +899,11 @@
       <c r="B7">
         <f>SUM(B4:B6)</f>
         <v>28.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="40.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="16" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -916,7 +921,7 @@
     <col min="4" max="4" width="14.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="12.140625" style="3"/>
     <col min="7" max="7" width="9.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="3" customWidth="1"/>
     <col min="9" max="9" width="17.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="12.140625" style="3"/>
@@ -1054,14 +1059,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="5"/>
       <c r="C7" s="4"/>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" s="14" t="s">
         <v>30</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1091,37 +1096,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="12" t="s">
+      <c r="A1" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="H1" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="I1" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="K1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="H1" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="L1" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="M1" s="12" t="s">
+      <c r="L1" s="11" t="s">
         <v>54</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -1150,10 +1155,10 @@
         <v>20</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -1161,31 +1166,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3">
         <v>41454</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H3" s="3">
         <v>2</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J3" s="3">
         <v>41454</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -1193,31 +1198,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3">
         <v>41460</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H4" s="3">
         <v>3</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J4" s="3">
         <v>41460</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -1225,31 +1230,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="3">
         <v>41470</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H5" s="3">
         <v>4</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J5" s="3">
         <v>41470</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -1257,31 +1262,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" s="3">
         <v>41486</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H6" s="3">
         <v>5</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J6" s="3">
         <v>41486</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -1289,36 +1294,36 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" s="3">
         <v>41558</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H7" s="3">
         <v>6</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J7" s="3">
         <v>41558</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L8" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M8" s="15"/>
     </row>
